--- a/reports/Debug-purgatory-20260111/For The Day (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Day (Actual)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Coaster</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -448,10 +448,10 @@
         <v>46033</v>
       </c>
       <c r="C3" s="2">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,10 +462,10 @@
         <v>46033</v>
       </c>
       <c r="C4" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,7 +476,7 @@
         <v>46033</v>
       </c>
       <c r="C5" s="2">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,7 +490,7 @@
         <v>46033</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>46033</v>
       </c>
       <c r="C7" s="2">
-        <v>533</v>
+        <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,7 +518,7 @@
         <v>46033</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,7 +532,7 @@
         <v>46033</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,10 +546,10 @@
         <v>46033</v>
       </c>
       <c r="C10" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>46033</v>
       </c>
       <c r="C11" s="2">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,7 +574,7 @@
         <v>46033</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>1375</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -588,7 +588,7 @@
         <v>46033</v>
       </c>
       <c r="C13" s="2">
-        <v>1375</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,7 +602,7 @@
         <v>46033</v>
       </c>
       <c r="C14" s="2">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
